--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N91_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.1642999917073</v>
+        <v>4.739198748652436</v>
       </c>
       <c r="D2" t="n">
-        <v>26.24718770920079</v>
+        <v>4.26516800274513</v>
       </c>
       <c r="E2" t="n">
-        <v>10.15629073490621</v>
+        <v>1.65039724442226</v>
       </c>
       <c r="F2" t="n">
-        <v>7.203186016690977</v>
+        <v>1.170517727712284</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.851718521894874</v>
+        <v>1.438404259807917</v>
       </c>
       <c r="D3" t="n">
-        <v>11.84081567581884</v>
+        <v>1.924132547320561</v>
       </c>
       <c r="E3" t="n">
-        <v>10.15629073490621</v>
+        <v>1.65039724442226</v>
       </c>
       <c r="F3" t="n">
-        <v>7.203186016690977</v>
+        <v>1.170517727712284</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
